--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-payment-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-payment-ncins-pa.xlsx
@@ -11,6 +11,7 @@
     <sheet name="1. Согласование" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2. Минимальная информация" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="3. Полная информация" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="BPMN методы (источник)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,34 +30,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="12"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4F6F7"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -73,27 +76,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -461,10 +472,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,7 +493,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
@@ -509,18 +525,14 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Назначение: Оплата страховки</t>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Назначение: Оплата страховки. Источник правды: BPMN ump-payment-ncins-pa.bpmn (PR NCINS). Timer PT5M. EQ — MOCK/DRAFT.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -531,11 +543,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -548,12 +564,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1 Согласование</t>
         </is>
@@ -584,11 +600,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -604,7 +615,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -620,249 +631,251 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1. Минимальная информация для определения необходимости проведения НТ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Пререквизит</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Пример</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Где взять</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Предпочтительная роль заполняющего</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="108" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="6" ht="98" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Описание алгоритма работы тестируемого метода</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>[ump-payment-ncins-pa]: Start → get-application-data → [DRAFT/MOCK] set-hold (Job ump-payment-ncins-pa.set-hold) → [DRAFT/MOCK] create-payment (Job ump-payment-ncins-pa.create-payment) → Receive paymentFinished (Kafka ump.process.from.system) → End. Timer P5M → BANK_REJECT. DRAFT prod-интеграции не актуальны; EQ замокан.</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>[ump-payment-ncins-pa] (BPMN):
+1) Start → get-application-data (businessKey DYNAMIC; processType контекст PAYMENT)
+2) Job ump-payment-ncins-pa.set-hold — DRAFT/MOCK
+3) Job ump-payment-ncins-pa.create-payment — DRAFT/MOCK
+4) Receive Message paymentFinished (Kafka ump.process.from.system); correlationKey = businessKey+"."+"NON_CREDIT_INSURANCE"
+5) End SUCCESS
+Event SubProcess Timer PT5M → BANK_REJECT.
+Delete при timeout выполняет main (XOR по timeoutMessage).</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>BPMN; запуск из main после signing</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Ссылка на алгоритм работы метода в git или confluence.</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>SLA по времени отклика</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>hold/create-payment — синхронные (несколько секунд). message-wait — асинхронный, в реальности почти мгновенно; запас СА ~30 сек. Таймер 5 мин.</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>sync несколько сек; async ~мгновенно (+30с запас)</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>hold/create — sync несколько секунд (мок). message-wait — почти мгновенно; запас СА ~30 сек. Таймер BPMN PT5M.</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>sync несколько сек; async ~0–30с; timer PT5M</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Получить от заказчика доработки. Если заказчик неизвестен, определяем экспертно.</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Частота планируемой нагрузки (ЧПН)</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>≈85/час среднее, ≈170/час макс (15000/мес минус доля signing-timeout ~5%). Параметризации/дублей нет: 1 инстанс=1 заявка.</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>≈85/час среднее, ≈170/час макс (15000×~95% после signing-timeout). 1 инстанс = 1 заявка.</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>15000×~95%</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Аналитику нужно определить: 1) макс вызовов/час; 2) среднее вызовов/час; 3) способ получения оценки.</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Само НТ проводится по профилю прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>[GET /applications/{id}] ~85–170/час
-[EQ hold / create-payment] ~85–170/час (МОК)
-[Kafka ump.process.from.system paymentFinished] ~85–170/час (подкладываем на НТ)</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Зависимости: EQ + Kafka</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>[get-application-data] ~85–170/час
+[EQ hold / create-payment MOCK] ~85–170/час
+[Kafka paymentFinished] ~85–170/час (подкладываем на НТ)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>EQ + Kafka</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Может совпадать с ЧПН.</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Может совпадать с прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -878,7 +891,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -894,284 +907,545 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2. Полная информация для проведения НТ (заполняется, только если получено заключение от инженера о необходимости проведения НТ)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Пререквизит</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Пример</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Где взять</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Предпочтительная роль заполняющего</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Пример кода вызова тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Включается автоматически через main BPMN после signing. Вход: businessKey (DYNAMIC), productCode=NON_CREDIT_INSURANCE.
-Реальных EQ-контрактов нет (мок). Моковый success: code=SUCCESS, message=null.
-Нужно подложить сообщение о завершении оплаты в Kafka; остальное на моках.</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Сценарий: get data → 2 мока → подложить paymentFinished</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Включается из main после signing. Вход: businessKey, productCode=NON_CREDIT_INSURANCE.
+Данные заявки (get): fullName, productId, inn, contractNumber, insurancePremium, debitAccount.
+Мок EQ: code=SUCCESS, message=null.
+Подложить paymentFinished с correlationKey="&lt;businessKey&gt;.NON_CREDIT_INSURANCE".</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>get → 2 мока → Kafka paymentFinished</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Тестировщик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Примеры кода ответа тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Мок: code=SUCCESS, message=null.
-Негативные 4xx/5xx EQ пока не обязательны (mock-only). Timeout/no-message — через timer P5M.</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>SUCCESS / BANK_REJECT по таймеру</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Мок: code=SUCCESS, message=null. Негативы EQ 4xx/5xx пока не обязательны (mock-only). Timeout — PT5M → BANK_REJECT.</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SUCCESS / BANK_REJECT</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Нужны примеры ответов, которые можно считать ожидаемыми.</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Изменяемые данные в рамках работы метода</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Отдельной параметризации нет. Изменения UMP — по факту get/маппинг заявки; EQ мок ничего в UMP не пишет. Дублей быть не может.</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Данные в рамках работы метода существенных изменений UMP DB не описывались</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Отдельной параметризации нет. EQ мок в UMP ничего не пишет. Дублей быть не может.</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Существенных изменений UMP DB не описывалось</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Перечислить поля/таблицы/ресурсы, которые создаются/перезаписываются (кроме логирования).</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Скрипт, содержащий сопутствующие изменения в БД (миграция)</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Нет необходимости</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Опционально. Скрипт готовит разработчик только однажды перед боем.</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Заглушки для внешних зависимостей</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>EQ полностью замокан (включение через поток main после signing). Kafka completion — подкладываем (в проде слал бы EQ). Говорить о живом контракте EQ сейчас бессмысленно.</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Мок EQ + ручной Kafka publish paymentFinished</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>EQ полностью замокан. Kafka completion подкладываем (в проде слал бы EQ). Живой контракт EQ сейчас неактуален.</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Мок EQ + Kafka paymentFinished</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Для зависимостей, которые нужно/можно глушить — прикрепить моки.</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Ожидаемое время отклика замоканных внешних зависимостей</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Hold/create mock: sync несколько секунд. Payment message: почти мгновенно (+запас 30с).</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>мок EQ ~несколько сек; message ~0–30с</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Hold/create mock: несколько секунд. Payment message: почти мгновенно (+запас 30с).</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>мок EQ ~несколько сек; message 0–30с</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Потребуется для имитации нагрузки на внешние зависимости.</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Сценарий тестирования</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>1) Success: get→mock hold→mock create→подложить paymentFinished→SUCCESS.
-2) Timeout: не публиковать сообщение→P5M→BANK_REJECT.
-Отдельного набора кейсов от Жени нет — текущий flow mock-only.</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>1) Success: get→mock hold→mock create→подложить paymentFinished (corr=businessKey.NON_CREDIT_INSURANCE)→SUCCESS.
+2) Timeout: не публиковать → PT5M → BANK_REJECT; main → delete.</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Основной + timeout</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Опционально. Готовит аналитик, если тестируется бизнес-процесс, а не метод.</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>НТ пререквизиты :: Worker ump-payment-ncins-pa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Шаги из ump-payment-ncins-pa.bpmn — STATIC vs DYNAMIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>BPMN id</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Type / called process</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Ключевые параметры</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>STATIC / DYNAMIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="50" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>startEvent</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>businessKey, productCode</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>DYNAMIC start</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="50" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>service-task-get-params</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Получить данные</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>get-application-data</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>данные для оплаты</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>DYNAMIC businessKey</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>set-hold</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Установить холд</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>ump-payment-ncins-pa.set-hold</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>DRAFT/MOCK EQ</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>MOCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>create-payment</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Создать ПП</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>ump-payment-ncins-pa.create-payment</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>DRAFT/MOCK EQ</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>MOCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>message-catch</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>paymentFinished</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>message intermediateCatch / ump.process.from.system</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>correlationKey=businessKey+"."+"NON_CREDIT_INSURANCE"</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>STATIC product in FEEL; DYNAMIC businessKey</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>EventSubProcess</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Timeout</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>timer PT5M → BANK_REJECT</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>forcefullyTerminate</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>STATIC PT5M</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-payment-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-payment-ncins-pa.xlsx
@@ -11,7 +11,7 @@
     <sheet name="1. Согласование" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2. Минимальная информация" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="3. Полная информация" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="BPMN методы (источник)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Методы и примеры (код)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +104,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -477,7 +478,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -493,7 +494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -525,10 +526,10 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="55" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Назначение: Оплата страховки. Источник правды: BPMN ump-payment-ncins-pa.bpmn (PR NCINS). Timer PT5M. EQ — MOCK/DRAFT.</t>
+          <t>BPMN payment + InsurancePaymentWorker (STUB hold/create) + ApplicationDataWorker. Timer в develop: PT15M.</t>
         </is>
       </c>
     </row>
@@ -548,7 +549,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -564,7 +565,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -615,7 +616,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -631,7 +632,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -674,202 +675,200 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="98" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Описание алгоритма работы тестируемого метода</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>[ump-payment-ncins-pa] (BPMN):
-1) Start → get-application-data (businessKey DYNAMIC; processType контекст PAYMENT)
-2) Job ump-payment-ncins-pa.set-hold — DRAFT/MOCK
-3) Job ump-payment-ncins-pa.create-payment — DRAFT/MOCK
-4) Receive Message paymentFinished (Kafka ump.process.from.system); correlationKey = businessKey+"."+"NON_CREDIT_INSURANCE"
-5) End SUCCESS
-Event SubProcess Timer PT5M → BANK_REJECT.
-Delete при timeout выполняет main (XOR по timeoutMessage).</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>BPMN; запуск из main после signing</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>1) get-application-data (PAYMENT) → ApplicationDataWorker
+2) ump-payment-ncins-pa.set-hold → InsurancePaymentWorker → PaymentService STUB
+3) ump-payment-ncins-pa.create-payment → STUB
+4) receive paymentFinished (corr=businessKey в develop)
+5) Event SubProcess timer PT15M → timeoutMessage=TIMEOUT</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>ump-payment-ncins-pa.bpmn + InsurancePaymentWorker</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Ссылка на алгоритм работы метода в git или confluence.</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>SLA по времени отклика</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>hold/create — sync несколько секунд (мок). message-wait — почти мгновенно; запас СА ~30 сек. Таймер BPMN PT5M.</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>sync несколько сек; async ~0–30с; timer PT5M</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Hold/create stub — мгновенно. Message почти мгновенно. Timer BPMN develop = PT15M.</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>PT15M в develop</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Получить от заказчика доработки. Если заказчик неизвестен, определяем экспертно.</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Частота планируемой нагрузки (ЧПН)</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>≈85/час среднее, ≈170/час макс (15000×~95% после signing-timeout). 1 инстанс = 1 заявка.</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>≈85/час / пик ≈170 (после signing-timeout).</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>15000×~95%</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Аналитику нужно определить: 1) макс вызовов/час; 2) среднее вызовов/час; 3) способ получения оценки.</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Само НТ проводится по профилю прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>[get-application-data] ~85–170/час
-[EQ hold / create-payment MOCK] ~85–170/час
-[Kafka paymentFinished] ~85–170/час (подкладываем на НТ)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>EQ + Kafka</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>[GET applications] ~85–170
+[set-hold STUB] ~85–170
+[create-payment STUB] ~85–170
+[paymentFinished message] ~85–170</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>EQ HTTP в коде нет</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Может совпадать с ЧПН.</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Может совпадать с прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
@@ -891,7 +890,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -907,7 +906,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -950,229 +949,231 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Пример кода вызова тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Включается из main после signing. Вход: businessKey, productCode=NON_CREDIT_INSURANCE.
-Данные заявки (get): fullName, productId, inn, contractNumber, insurancePremium, debitAccount.
-Мок EQ: code=SUCCESS, message=null.
-Подложить paymentFinished с correlationKey="&lt;businessKey&gt;.NON_CREDIT_INSURANCE".</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>get → 2 мока → Kafka paymentFinished</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>get PAYMENT outs: fullName, productId, inn, contractNumber, insurancePremium, debitAccount.
+set-hold / create-payment vars (IT): {"businessKey":"550e8400-e29b-41d4-a716-446655110003","productCode":"NON_INSURANCE_CODE","systemCode":"SFA"}
+HTTP EQ отсутствует — PaymentService TODO заглушка.</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>InsurancePaymentWorkerIT</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Тестировщик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Примеры кода ответа тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Мок: code=SUCCESS, message=null. Негативы EQ 4xx/5xx пока не обязательны (mock-only). Timeout — PT5M → BANK_REJECT.</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>SUCCESS / BANK_REJECT</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>set-hold / create-payment: {"code":"SUCCESS"} (message null).
+На ERROR маппер отдаёт code=ERROR + message.
+Timeout: timeoutMessage=TIMEOUT (PT15M).</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>{"code":"SUCCESS"}</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Нужны примеры ответов, которые можно считать ожидаемыми.</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Изменяемые данные в рамках работы метода</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Отдельной параметризации нет. EQ мок в UMP ничего не пишет. Дублей быть не может.</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Существенных изменений UMP DB не описывалось</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Stub ничего не пишет. UMP DB не меняется этим воркером.</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>нет изменений</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Перечислить поля/таблицы/ресурсы, которые создаются/перезаписываются (кроме логирования).</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Скрипт, содержащий сопутствующие изменения в БД (миграция)</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Нет необходимости</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Опционально. Скрипт готовит разработчик только однажды перед боем.</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Заглушки для внешних зависимостей</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>EQ полностью замокан. Kafka completion подкладываем (в проде слал бы EQ). Живой контракт EQ сейчас неактуален.</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Мок EQ + Kafka paymentFinished</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Hold/create уже stub в коде. paymentFinished — подложить Zeebe/Kafka message (corr=businessKey).</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>PaymentService stub</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Для зависимостей, которые нужно/можно глушить — прикрепить моки.</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Ожидаемое время отклика замоканных внешних зависимостей</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Hold/create mock: несколько секунд. Payment message: почти мгновенно (+запас 30с).</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>мок EQ ~несколько сек; message 0–30с</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Stub ~0; message 0–30с запас.</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>мгновенно</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Потребуется для имитации нагрузки на внешние зависимости.</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Сценарий тестирования</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>1) Success: get→mock hold→mock create→подложить paymentFinished (corr=businessKey.NON_CREDIT_INSURANCE)→SUCCESS.
-2) Timeout: не публиковать → PT5M → BANK_REJECT; main → delete.</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Основной + timeout</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>1) Success: get→set-hold→create-payment→paymentFinished.
+2) Timeout PT15M без message.
+После реальной EQ — обновить контракты.</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>IT: InsurancePaymentWorkerIT</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Опционально. Готовит аналитик, если тестируется бизнес-процесс, а не метод.</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
@@ -1189,15 +1190,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1210,14 +1211,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Шаги из ump-payment-ncins-pa.bpmn — STATIC vs DYNAMIC</t>
+          <t>Методы payment (develop)</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1230,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>BPMN id</t>
+          <t>BPMN / JobWorker</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1239,209 +1240,177 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Type / called process</t>
+          <t>Type / HTTP</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Ключевые параметры</t>
+          <t>Request / Input</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>STATIC / DYNAMIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="50" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+          <t>Response / Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>startEvent</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>businessKey, productCode</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>DYNAMIC start</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="50" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>get-application-data</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>ApplicationDataWorker</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>GET /applications/{id}</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>processType=PAYMENT</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>fullName, productId, inn, contractNumber, insurancePremium, debitAccount</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>service-task-get-params</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Получить данные</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>get-application-data</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>данные для оплаты</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>DYNAMIC businessKey</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="50" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>ump-payment-ncins-pa.set-hold</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>InsurancePaymentWorker.setHold</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>STUB PaymentService</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Map variables</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>{"code":"SUCCESS"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>set-hold</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Установить холд</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>ump-payment-ncins-pa.set-hold</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>DRAFT/MOCK EQ</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>MOCK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>ump-payment-ncins-pa.create-payment</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>InsurancePaymentWorker.createPayment</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>STUB PaymentService</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Map variables</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>{"code":"SUCCESS"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>create-payment</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Создать ПП</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>ump-payment-ncins-pa.create-payment</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>DRAFT/MOCK EQ</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>MOCK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="50" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>message paymentFinished</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Zeebe receive</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>corr=businessKey</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>payload TBD</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>End / continue</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>message-catch</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>paymentFinished</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>message intermediateCatch / ump.process.from.system</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>correlationKey=businessKey+"."+"NON_CREDIT_INSURANCE"</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>STATIC product in FEEL; DYNAMIC businessKey</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>EventSubProcess</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Timeout</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>timer PT5M → BANK_REJECT</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>forcefullyTerminate</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>STATIC PT5M</t>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>timer</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>event sub-process</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>PT15M</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>timeoutMessage=TIMEOUT</t>
         </is>
       </c>
     </row>

--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-payment-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-payment-ncins-pa.xlsx
@@ -885,7 +885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -906,7 +906,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · п.6/п.7 в формате образца onboarding (Map.of)</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
+    <row r="6" ht="220" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>6</t>
@@ -962,19 +962,52 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>get PAYMENT outs: fullName, productId, inn, contractNumber, insurancePremium, debitAccount.
-set-hold / create-payment vars (IT): {"businessKey":"550e8400-e29b-41d4-a716-446655110003","productCode":"NON_INSURANCE_CODE","systemCode":"SFA"}
-HTTP EQ отсутствует — PaymentService TODO заглушка.</t>
+          <t xml:space="preserve">У воркера отсутствует HTTP-эндпоинт.
+Вызов происходит напрямую в Camunda.
+Camunda на базе Java скрипта, инструкция — https://confluence.moscow.alfaintra.net/pages/viewpage.action?pageId=2136656813
+Пример запроса:
+Map&lt;String, Object&gt; variables = Map.of(
+  "businessKey", "550e8400-e29b-41d4-a716-446655110003", // id заявки (UMP application)
+  "productCode", "NON_CREDIT_INSURANCE" // const
+);
+final ProcessInstanceEvent processInstanceEvent = client
+  .newCreateInstanceCommand()
+  .bpmnProcessId("ump-payment-ncins-pa")
+  .latestVersion()
+  .variables(variables)
+  .send()
+  .join();
+Параметры для запроса:
+1. businessKey — UUID заявки (параметризовать на объём ≥ ЧПН)
+2. productCode — const NON_CREDIT_INSURANCE (параметризация не нужна)
+--- Шаги (InsurancePaymentWorkerIT) ---
+1) get-application-data processType=PAYMENT
+Map.of("businessKey", "550e8400-e29b-41d4-a716-446655110003", "processType", "PAYMENT");
+HTTP: GET .../applications/550e8400-e29b-41d4-a716-446655110003?include=PARTICIPANT&amp;include=PRODUCT
+2) set-hold type=ump-payment-ncins-pa.set-hold
+Map.of(
+  "businessKey", "550e8400-e29b-41d4-a716-446655110003",
+  "productCode", "NON_CREDIT_INSURANCE",
+  "systemCode", "SFA"
+);
+HTTP: отсутствует (PaymentService TODO stub)
+3) create-payment type=ump-payment-ncins-pa.create-payment
+те же variables; HTTP отсутствует (stub)
+4) Receive paymentFinished, correlationKey=businessKey (develop)
+JSON payload — TBD (добыть на стенде / подложить пустой/минимальный message)
+</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>InsurancePaymentWorkerIT</t>
+          <t>Map.of(...); stub без HTTP; message paymentFinished TBD</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.</t>
+          <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.
+Параметризовать businessKey (≥ ЧПН). productCode — const NON_CREDIT_INSURANCE.
+Источник примеров: develop ump-ncins-pa *WorkerIT + stubs.</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -983,7 +1016,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
+    <row r="7" ht="180" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>7</t>
@@ -996,19 +1029,27 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>set-hold / create-payment: {"code":"SUCCESS"} (message null).
-На ERROR маппер отдаёт code=ERROR + message.
-Timeout: timeoutMessage=TIMEOUT (PT15M).</t>
+          <t>set-hold / create-payment (stub):
+{ "code": "SUCCESS" }
+// message = null
+При ошибке маппера:
+{ "code": "ERROR", "message": "&lt;text&gt;" }
+get-application-data: getProcessParams = SUCCESS | ERROR
+(+ fullName, productId, inn, contractNumber, insurancePremium, debitAccount)
+Timeout event sub-process (PT15M): timeoutMessage = "TIMEOUT"
+HTTP EQ в develop нет — негативы 4xx/5xx пока не применимы.</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>{"code":"SUCCESS"}</t>
+          <t>{"code":"SUCCESS"} / TIMEOUT</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Нужны примеры ответов, которые можно считать ожидаемыми.</t>
+          <t>Нужны примеры ответов, которые можно считать ожидаемыми.
+Например: getProcessParams=SUCCESS; HTTP 200/201; result=SUCCESS.
+Источник: *WorkerIT + stubs/ump/ump_application_response_200.json.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1179,6 +1220,14 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-payment-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-payment-ncins-pa.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,10 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -93,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,6 +110,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -494,7 +501,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -565,7 +572,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -632,7 +639,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -885,7 +892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -906,7 +913,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · п.6/п.7 в формате образца onboarding (Map.of)</t>
+          <t>UMP · п.6/п.7 в формате образца onboarding (Map.of) · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -1220,14 +1227,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1239,15 +1238,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1260,14 +1259,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>Полные request/response (не только имя метода). Источник: develop ump-ncins-pa@4a921a1653e + *WorkerIT + stubs. · полные HTTP body</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Методы payment (develop)</t>
+          <t>HTTP / JobWorker — полные тела запросов и ответов</t>
         </is>
       </c>
     </row>
@@ -1279,187 +1278,329 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>BPMN / JobWorker</t>
+          <t>Метод / JobWorker</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Где</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Type / HTTP</t>
+          <t>Полный REQUEST (headers + body)</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Request / Input</t>
+          <t>Полный RESPONSE (status + body)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Response / Output</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+          <t>Источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="420" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>get-application-data</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>ApplicationDataWorker</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>GET /applications/{id}</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>processType=PAYMENT</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>fullName, productId, inn, contractNumber, insurancePremium, debitAccount</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>ump-payment-ncins-pa.set-hold</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>InsurancePaymentWorker.setHold</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>STUB PaymentService</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Map variables</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>{"code":"SUCCESS"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>ump-payment-ncins-pa.create-payment</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>InsurancePaymentWorker.createPayment</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>STUB PaymentService</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Map variables</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>{"code":"SUCCESS"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>get-application-data
+GET /applications/{id}</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>ApplicationDataWorker
+все процессы</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>GET /applications/6dc5daf3-da12-4aae-9766-572da7b6b003?include=PARTICIPANT&amp;include=PRODUCT HTTP/1.1
+Host: ump-application-facade.ump.svc.cluster.local
+Accept: application/json
+(без body)
+Camunda job input:
+{
+  "businessKey": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+  "processType": "&lt;PREPARE_DOCUMENTS|SIGNING|PAYMENT|FINALISATION|DELETE_DOCS&gt;"
+}</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>HTTP/1.1 200 OK
+Content-Type: application/json
+{
+  "externalApplicationIds": [
+    {
+      "extAppId": "7ca85f64-5717-4562-b3fc-6c163f65aba9",
+      "systemCode": "SFA",
+      "extAppCreateDate": "2026-06-25T12:45:34.785179Z"
+    }
+  ],
+  "channels": [
+    {
+      "id": "bd458000-77c2-48af-91b4-815f7ef2d4e6",
+      "userInfo": {
+        "userId": "f6753df0-b5c9-4828-a7b7-f9f3f7d8f33c",
+        "login": "service-account-nib-corp-ncins"
+      },
+      "code": "nib-corp-ncins",
+      "name": "НИБ. Страхование",
+      "isDeleted": false,
+      "category": "RECEIVE",
+      "type": "BANK_SYSTEM"
+    }
+  ],
+  "participants": [
+    {
+      "id": "bdec62a5-e10a-4c5b-86c7-b5ac190b8055",
+      "applicationId": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+      "isDeleted": false,
+      "contacts": [
+        {
+          "type": "EMAIL",
+          "typeName": "Email",
+          "value": "romashka@rambler.ru",
+          "isPrimary": false
+        },
+        {
+          "type": "PHONE",
+          "typeName": "Телефон",
+          "value": "79183221488",
+          "isPrimary": false
+        }
+      ],
+      "addresses": [
+        {
+          "type": "FACT",
+          "typeName": "Адрес проживания / фактический - краткий",
+          "address": {
+            "fullAddress": "Г. Пушкино ул. Колотушкина д. 14/88"
+          }
+        }
+      ],
+      "identityDocuments": [],
+      "okveds": [],
+      "licenses": [],
+      "management": [],
+      "founders": [],
+      "externalPins": [],
+      "pin": "AAAXYX",
+      "type": "LEGAL",
+      "typeName": "Юридическое лицо",
+      "fullName": "ООО Звезда",
+      "inn": "7826688577",
+      "createDate": "2026-07-09T17:19:18.963685Z",
+      "lastUpdateDate": "2026-07-09T17:19:19.99786Z",
+      "citizenship": "Россия",
+      "citizenshipCode": "RU",
+      "taxCountryCode": "RU",
+      "ogrn": "1027810281740"
+    }
+  ],
+  "products": [
+    {
+      "id": "3d9fe175-2bc5-442a-b900-48522551de3f",
+      "applicationId": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+      "status": {
+        "isTerminate": true,
+        "code": "COMPLETE",
+        "name": "Завершен"
+      },
+      "stage": {
+        "code": "PAYMENT_COMPLETED",
+        "name": "PAYMENT_COMPLETED"
+      },
+      "createDate": "2026-07-09T17:19:18.891861Z",
+      "lastUpdateDate": "2026-07-09T17:23:50.600316Z",
+      "code": "NON_CREDIT_INSURANCE",
+      "name": "Некредитное страхование ЮЛ",
+      "type": "PRODUCT",
+      "main": false,
+      "isDeleted": false,
+      "responsibleManager": {
+        "login": "U_M13RU"
+      },
+      "salesChannel": {
+        "code": "SFA",
+        "name": "SFA"
+      },
+      "productProperties": {
+        "programId": 1073741824,
+        "beginDate": "2026-06-25T11:47:13.57Z",
+        "endDate": "2026-06-25T11:47:13.57Z",
+        "signDate": "2026-06-25T11:47:13.57Z",
+        "duration": 12,
+        "insuranceSum": 20000.0,
+        "insurancePremium": 20000.0,
+        "contractNumber": "1423423/sdf/123",
+        "paymentType": "payment_account",
+        "agreementLink": "7ca85f64-5717-4562-b3fc-6c163f65aba9",
+        "insuranceObjects": [
+          {
+            "paymentAccount": "123523464567347"
+          }
+        ],
+        "code": "NON_CREDIT_INSURANCE"
+      },
+      "channelCode": "nib-corp-ncins"
+    }
+  ],
+  "options": [],
+  "id": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+  "createDate": "2026-07-09T17:19:18.833504Z",
+  "lastUpdateDate": "2026-07-09T17:22:46.462517Z",
+  "number": "UMP26070994592",
+  "statusCode": "COMPLETE",
+  "statusName": "Завершена",
+  "finalVersion": true,
+  "isDeleted": false
+}
+Camunda job output (успех):
+{ "getProcessParams": "SUCCESS", ...поля по processType из ApplicationMapper }
+Ошибка:
+{ "getProcessParams": "ERROR" }</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>ApplicationDataWorkerIT
+stubs/ump/ump_application_response_200.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="140" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>ump-payment-ncins-pa.set-hold
+STUB (нет HTTP)</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>InsurancePaymentWorker
+payment</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>JobWorker: ump-payment-ncins-pa.set-hold
+HTTP: нет (PaymentService TODO stub)
+Camunda input (InsurancePaymentWorkerIT):
+{
+  "businessKey": "550e8400-e29b-41d4-a716-446655110003",
+  "productCode": "NON_CREDIT_INSURANCE",
+  "systemCode": "SFA"
+}</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Camunda output:
+{
+  "code": "SUCCESS"
+}
+// message = null
+Ошибка:
+{ "code": "ERROR", "message": "&lt;text&gt;" }</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>InsurancePaymentWorkerIT
+PaymentService stub</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>ump-payment-ncins-pa.create-payment
+STUB (нет HTTP)</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>InsurancePaymentWorker
+payment</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>JobWorker: ump-payment-ncins-pa.create-payment
+HTTP: нет (PaymentService TODO stub)
+Camunda input: тот же Map, что для set-hold (см. выше).</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Camunda output:
+{
+  "code": "SUCCESS"
+}
+// message = null
+Ошибка:
+{ "code": "ERROR", "message": "&lt;text&gt;" }</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>InsurancePaymentWorkerIT
+PaymentService stub</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>message paymentFinished</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Zeebe receive</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>corr=businessKey</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>payload TBD</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>End / continue</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>timer</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>event sub-process</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>PT15M</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>timeoutMessage=TIMEOUT</t>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Zeebe receive
+payment</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>correlationKey = businessKey (develop BPMN)
+Полный JSON payload сообщения — TBD (в репе нет; добыть на стенде).
+Минимально для НТ: опубликовать completion с corr = businessKey.</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Продолжение процесса / End.
+Timeout PT15M → timeoutMessage=TIMEOUT</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>BPMN ump-payment-ncins-pa</t>
         </is>
       </c>
     </row>
